--- a/SINGLE HADITH CONTENT/missing_input/[V1] TARGIB WATTAHRIB-BANGLA_missing.xlsx
+++ b/SINGLE HADITH CONTENT/missing_input/[V1] TARGIB WATTAHRIB-BANGLA_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,23 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>(صحيح) عَنْ أبِيْ هُرَيْرَةَ رَضِيَ اللَّهُ عَنْهُ قَالَ: قَالَ رَسُولُ اللَّهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ مَنْ سُئِلَ عَنْ عِلْمٍ فَكَتَمَهُ أُلْجِمَ يَوْمَ الْقِيَامَةِ بِلِجَامٍ مِنْ نَارٍ. رواه أبو داود والترمذي وحسنه وابن ماجه وابن حبان في صحيحه والبيهقي ورواه الحاكم</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, রাসূলুল্লাহ (সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম) বলেছেনঃ “কেউ যদি কোন বিষয়ের ইলম সম্পর্কে জিজ্ঞাসিত হয়, আর সে তা গোপন রাখে, তবে ক্বিয়ামত দিবসে তার মুখে আগুনের লাগাম পরানো হবে।” (হাদীছটি বর্ণনা করেছেন আবু দাউদ, তিরমিযী, ইবনে মাজাহ, ইবনে হিব্বান, বায়হাক্বী এবং অনুরূপ বাক্যে হাকেম। হাকেম বলেনঃ হাদীছটি বুখারী ও মুসলিমের শর্তনুযায়ী ছহীহ, কিন্তু তাঁরা তা নিজেদের পুস্তকে উল্লেখ করেন নি।) ইবনে মাজাহর অপর বর্ণনায়ঃ مَا مِنْ رَجُلٍ يَحْفَظُ عِلْمًا فَيَكْتُمُهُ إِلَّا أَتَي يَوْمَ الْقِيَامَةِ مَلْجُوْمًا بِلِجَامٍ مِنْ النَّارِ “কোন মানুষ যদি কোন বিষয়ে জ্ঞান রাখে আর সে তা গোপন করে। তবে সে ক্বিয়ামত দিবসে আগুনের লাগাম পরানো অবস্থায় উপস্থিত হবে।"</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
